--- a/data/trans_dic/P25D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,53</t>
+          <t>0,71; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,03; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,97</t>
+          <t>0,52; 2,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,27</t>
+          <t>0,31; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,96</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,15</t>
+          <t>0,4; 2,13</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,22</t>
+          <t>0,08; 1,12</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,95</t>
+          <t>0,2; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,34</t>
+          <t>0,21; 1,46</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,59</t>
+          <t>0,62; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,09</t>
+          <t>0,27; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,82</t>
+          <t>0,54; 1,9</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,5</t>
+          <t>0,41; 2,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,9</t>
+          <t>0,46; 1,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,88</t>
+          <t>0,58; 1,82</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,66</t>
+          <t>0,68; 1,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,97</t>
+          <t>0,42; 0,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,16</t>
+          <t>0,62; 1,15</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1801</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2386</t>
+          <t>0; 1837</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2199</t>
+          <t>0; 2400</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3159; 28683</t>
+          <t>3693; 27444</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 10082</t>
+          <t>155; 7242</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5501; 30726</t>
+          <t>5349; 30362</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1011; 10344</t>
+          <t>983; 11180</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>657; 6832</t>
+          <t>647; 6644</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2641; 14273</t>
+          <t>2665; 14174</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7594</t>
+          <t>0; 8320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4320</t>
+          <t>0; 5063</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>717; 9589</t>
+          <t>659; 8828</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3412</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>383; 4074</t>
+          <t>426; 3942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>794; 5172</t>
+          <t>815; 5641</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1391</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7248</t>
+          <t>0; 6995</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6290</t>
+          <t>0; 7161</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3957; 15941</t>
+          <t>3805; 15772</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2461; 17592</t>
+          <t>2235; 18137</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8152; 26563</t>
+          <t>7875; 27766</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4269; 23167</t>
+          <t>3814; 22290</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3065; 13662</t>
+          <t>3331; 13655</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9472; 30901</t>
+          <t>9515; 29866</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>23831; 57128</t>
+          <t>23553; 57918</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15475; 35432</t>
+          <t>15300; 36286</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44527; 82700</t>
+          <t>44134; 81536</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25D_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Provincia-trans_dic.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,48</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,29</t>
+          <t>0,79; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,41</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,94</t>
+          <t>0,56; 2,86</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,54</t>
+          <t>0,31; 3,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,9</t>
+          <t>0,19; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,13</t>
+          <t>0,43; 1,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,12</t>
+          <t>0,17; 2,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,89</t>
+          <t>0,19; 1,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,46</t>
+          <t>0,19; 1,27</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,56</t>
+          <t>0,6; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,15</t>
+          <t>0,54; 2,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,9</t>
+          <t>0,63; 1,88</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,4</t>
+          <t>0,74; 2,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,9</t>
+          <t>0,35; 1,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,82</t>
+          <t>0,73; 2,0</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,68</t>
+          <t>0,81; 1,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,99</t>
+          <t>0,48; 1,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,15</t>
+          <t>0,7; 1,27</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1837</t>
+          <t>0; 2726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2400</t>
+          <t>0; 3024</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13729</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3693; 27444</t>
+          <t>4166; 27773</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>155; 7242</t>
+          <t>0; 9708</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5349; 30362</t>
+          <t>5988; 30786</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6391</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>983; 11180</t>
+          <t>978; 11521</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>647; 6644</t>
+          <t>663; 6422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2665; 14174</t>
+          <t>2872; 13009</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>6288</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8320</t>
+          <t>0; 18934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5063</t>
+          <t>0; 3952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>659; 8828</t>
+          <t>1319; 21841</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2447</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 5236</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>426; 3942</t>
+          <t>422; 3823</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>815; 5641</t>
+          <t>807; 5517</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6995</t>
+          <t>0; 6560</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7161</t>
+          <t>0; 6447</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16924</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3805; 15772</t>
+          <t>4240; 16298</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2235; 18137</t>
+          <t>4153; 18238</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7875; 27766</t>
+          <t>9338; 27779</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>20504</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3814; 22290</t>
+          <t>5876; 22187</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3331; 13655</t>
+          <t>2909; 13791</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9515; 29866</t>
+          <t>11920; 32619</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>23553; 57918</t>
+          <t>28507; 62490</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15300; 36286</t>
+          <t>17746; 39041</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44134; 81536</t>
+          <t>50758; 92172</t>
         </is>
       </c>
     </row>
